--- a/artfynd/A 12443-2024 artfynd.xlsx
+++ b/artfynd/A 12443-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66380900</v>
+        <v>66380899</v>
       </c>
       <c r="B2" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595807.4091685121</v>
+        <v>595807</v>
       </c>
       <c r="R2" t="n">
-        <v>6565704.096738162</v>
+        <v>6565704</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2017-05-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-05-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66380899</v>
+        <v>126289337</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,14 +808,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mögsjön, SO om, Srm</t>
+          <t>Brantberget, Brantberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595807.4091685121</v>
+        <v>595976</v>
       </c>
       <c r="R3" t="n">
-        <v>6565704.096738162</v>
+        <v>6565522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +827,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Eskilstuna</t>
+          <t>Flen</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -857,27 +837,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Ärla</t>
+          <t>Dunker</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-05-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-05-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,36 +858,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrskog, sank</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Marcus Arnesson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Marcus Arnesson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66380887</v>
+        <v>66380900</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brattberget, V om, Srm</t>
+          <t>Mögsjön, SO om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595959.1660218789</v>
+        <v>595807</v>
       </c>
       <c r="R4" t="n">
-        <v>6565586.031114235</v>
+        <v>6565704</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,21 +942,11 @@
           <t>2017-05-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-05-28</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,7 +958,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrskog, sank</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1023,6 +973,108 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>66380887</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brattberget, V om, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595959</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6565586</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-05-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-05-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12443-2024 artfynd.xlsx
+++ b/artfynd/A 12443-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66380899</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126289337</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66380900</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,8 +1095,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66380887</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>